--- a/data/trans_dic/P6907S1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 20,16</t>
+          <t>2,25; 20,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 22,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,12</t>
+          <t>1,55; 14,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 19,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,9</t>
+          <t>0,0; 20,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 26,24</t>
+          <t>1,08; 26,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,17</t>
+          <t>2,67; 15,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,89</t>
+          <t>0,0; 15,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,53</t>
+          <t>2,03; 11,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,96</t>
+          <t>1,72; 15,51</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 19,12</t>
+          <t>2,62; 19,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,5</t>
+          <t>1,22; 10,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,98</t>
+          <t>2,51; 23,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,39</t>
+          <t>0,0; 18,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,87</t>
+          <t>0,0; 31,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,54</t>
+          <t>1,57; 13,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 15,15</t>
+          <t>2,83; 15,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,06</t>
+          <t>0,0; 15,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,77</t>
+          <t>0,81; 6,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 13,98</t>
+          <t>2,48; 13,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 24,6</t>
+          <t>2,65; 23,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,76</t>
+          <t>0,0; 34,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,24</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 26,64</t>
+          <t>7,0; 26,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,61</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,64</t>
+          <t>0,0; 28,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 28,38</t>
+          <t>9,6; 27,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 20,37</t>
+          <t>3,4; 19,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,29</t>
+          <t>0,0; 28,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,29</t>
+          <t>0,0; 15,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 23,6</t>
+          <t>10,14; 23,64</t>
         </is>
       </c>
     </row>
@@ -1137,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 16,39</t>
+          <t>1,75; 17,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,16</t>
+          <t>0,0; 45,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,3</t>
+          <t>0,0; 16,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,75</t>
+          <t>0,0; 34,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,15</t>
+          <t>0,0; 27,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,64</t>
+          <t>0,0; 55,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 15,3</t>
+          <t>2,62; 15,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,76</t>
+          <t>0,0; 33,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 15,54</t>
+          <t>0,51; 14,08</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 33,75</t>
+          <t>3,76; 29,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,59</t>
+          <t>0,0; 57,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,39</t>
+          <t>0,0; 15,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,98</t>
+          <t>0,0; 71,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 33,03</t>
+          <t>6,29; 33,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,57</t>
+          <t>0,0; 33,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 10,16</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 29,02</t>
+          <t>5,01; 28,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,74</t>
+          <t>0,0; 27,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 42,17</t>
+          <t>12,58; 42,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,2</t>
+          <t>0,0; 36,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,86</t>
+          <t>1,55; 15,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 22,88</t>
+          <t>5,48; 23,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,49</t>
+          <t>0,0; 20,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,44; 25,09</t>
+          <t>8,15; 25,37</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,6</t>
+          <t>6,27; 22,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,82</t>
+          <t>0,0; 10,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,91; 26,37</t>
+          <t>7,71; 26,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 28,4</t>
+          <t>6,78; 28,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 17,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,87</t>
+          <t>0,0; 11,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 30,08</t>
+          <t>11,27; 31,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 19,86</t>
+          <t>7,65; 20,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 8,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,17</t>
+          <t>0,82; 7,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,03; 24,83</t>
+          <t>10,62; 23,92</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,7</t>
+          <t>2,48; 11,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,63</t>
+          <t>0,0; 28,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,2; 26,21</t>
+          <t>8,13; 27,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>0,0; 10,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 13,94</t>
+          <t>4,95; 14,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,16</t>
+          <t>0,0; 17,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,13</t>
+          <t>6,84; 12,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 9,72</t>
+          <t>2,6; 10,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,03</t>
+          <t>1,76; 5,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,88; 15,11</t>
+          <t>7,76; 15,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,58</t>
+          <t>7,24; 16,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,73</t>
+          <t>0,86; 7,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,44</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,59</t>
+          <t>5,48; 11,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,22</t>
+          <t>7,53; 12,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,57</t>
+          <t>2,25; 7,74</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,76</t>
+          <t>1,85; 5,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,05</t>
+          <t>7,24; 12,19</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>973; 8639</t>
+          <t>962; 8936</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 3639</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>902; 8273</t>
+          <t>910; 8366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5283</t>
+          <t>0; 5563</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7729</t>
+          <t>0; 8230</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>159; 4134</t>
+          <t>170; 4224</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1917; 10837</t>
+          <t>1911; 11201</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4495</t>
+          <t>0; 4732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1876; 12461</t>
+          <t>2022; 11867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>668; 5957</t>
+          <t>684; 6176</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1893; 13844</t>
+          <t>1895; 14450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2427,52 +2427,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1000; 8694</t>
+          <t>1012; 8699</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10172</t>
+          <t>1161; 11039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6666</t>
+          <t>0; 6005</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4198</t>
+          <t>0; 5144</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>728; 6153</t>
+          <t>716; 6059</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3045; 15922</t>
+          <t>2969; 16350</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6100</t>
+          <t>0; 6126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1008; 8496</t>
+          <t>1019; 8575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2416; 12822</t>
+          <t>2276; 12779</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>972; 9009</t>
+          <t>970; 8571</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 4311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3607; 13183</t>
+          <t>3464; 13159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6433</t>
+          <t>0; 6014</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1614</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3581</t>
+          <t>0; 3595</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4507; 13033</t>
+          <t>4407; 12466</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2003; 11884</t>
+          <t>1983; 11186</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5045</t>
+          <t>0; 5050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 5277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9746; 22520</t>
+          <t>9679; 22555</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1046; 9559</t>
+          <t>1019; 10081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5086</t>
+          <t>0; 4145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4642</t>
+          <t>0; 5402</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 16039</t>
+          <t>0; 14112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6618</t>
+          <t>0; 6294</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4271</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2568; 12399</t>
+          <t>2127; 12571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5323</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4589</t>
+          <t>0; 4584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>731; 18807</t>
+          <t>612; 17037</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>882; 7747</t>
+          <t>863; 6777</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5982</t>
+          <t>0; 5900</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2733</t>
+          <t>0; 2724</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5017</t>
+          <t>0; 5002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1823</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1525</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 722</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1856; 9884</t>
+          <t>1883; 10128</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6757</t>
+          <t>0; 6306</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3093</t>
+          <t>0; 2921</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2084; 12134</t>
+          <t>2097; 11978</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1803</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5775</t>
+          <t>0; 6154</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4222; 13334</t>
+          <t>3977; 13374</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5102</t>
+          <t>0; 5077</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1558</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1727</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>455; 4489</t>
+          <t>467; 4790</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2830; 12788</t>
+          <t>3063; 13345</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1811</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5820</t>
+          <t>0; 6155</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5220; 15513</t>
+          <t>5038; 15687</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5528; 19992</t>
+          <t>5543; 19614</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1904</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 8475</t>
+          <t>0; 7926</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6523; 19297</t>
+          <t>5638; 19555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2822; 12365</t>
+          <t>2953; 12261</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4143</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 7166</t>
+          <t>0; 6426</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7252; 21213</t>
+          <t>7952; 22337</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10044; 26206</t>
+          <t>10096; 27484</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5240</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1102; 9605</t>
+          <t>1104; 10388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15853; 35687</t>
+          <t>15262; 34374</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2824; 12743</t>
+          <t>2704; 12920</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6451</t>
+          <t>0; 6332</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1974</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3087; 13047</t>
+          <t>4050; 13789</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 1919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 1936</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5944</t>
+          <t>0; 5723</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7917; 22118</t>
+          <t>7861; 22702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 6853</t>
+          <t>0; 6278</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 6176</t>
+          <t>0; 6654</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>31374; 57283</t>
+          <t>32292; 57892</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3828; 13864</t>
+          <t>3708; 15108</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6822; 21090</t>
+          <t>6155; 20359</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26759; 51294</t>
+          <t>26360; 51777</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16145; 34298</t>
+          <t>15931; 35361</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>901; 7739</t>
+          <t>865; 7292</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1873; 11770</t>
+          <t>1914; 12838</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19193; 41055</t>
+          <t>19415; 41707</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>52223; 84638</t>
+          <t>52127; 84594</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5690; 18377</t>
+          <t>5467; 18786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10744; 26956</t>
+          <t>10465; 29009</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49477; 83611</t>
+          <t>50220; 84552</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6907S1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,86</t>
+          <t>2,25; 20,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,69</t>
+          <t>0,0; 23,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,28</t>
+          <t>1,53; 13,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>0,0; 15,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,44</t>
+          <t>0,0; 15,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,13</t>
+          <t>0,0; 19,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 26,81</t>
+          <t>3,36; 26,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 15,67</t>
+          <t>2,62; 15,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,68</t>
+          <t>0,0; 14,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,93</t>
+          <t>2,04; 12,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,51</t>
+          <t>1,48; 15,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 19,96</t>
+          <t>2,62; 20,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,88</t>
+          <t>0,0; 28,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,51</t>
+          <t>1,23; 10,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 23,85</t>
+          <t>2,37; 22,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,37</t>
+          <t>0,0; 21,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 26,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,33</t>
+          <t>1,55; 13,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,56</t>
+          <t>2,95; 15,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,12</t>
+          <t>0,0; 15,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,83</t>
+          <t>0,8; 6,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,93</t>
+          <t>2,99; 15,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 23,41</t>
+          <t>2,75; 24,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,37</t>
+          <t>0,0; 42,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,28</t>
+          <t>0,0; 17,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 26,59</t>
+          <t>7,14; 25,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,68</t>
+          <t>0,0; 27,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,76</t>
+          <t>0,0; 35,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 27,14</t>
+          <t>9,33; 26,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 19,17</t>
+          <t>3,52; 20,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,32</t>
+          <t>0,0; 28,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,63</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 23,64</t>
+          <t>9,74; 22,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 17,29</t>
+          <t>1,68; 17,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,77</t>
+          <t>0,0; 45,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,64</t>
+          <t>0,0; 14,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,97</t>
+          <t>0,0; 32,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,72</t>
+          <t>0,0; 30,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,23</t>
+          <t>0,0; 50,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 15,51</t>
+          <t>2,62; 14,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,38</t>
+          <t>0,0; 42,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 14,08</t>
+          <t>0,88; 17,92</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 29,52</t>
+          <t>3,7; 29,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,78</t>
+          <t>0,0; 51,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,34</t>
+          <t>0,0; 11,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,76</t>
+          <t>0,0; 71,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 33,84</t>
+          <t>6,12; 33,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,2</t>
+          <t>0,0; 32,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,16</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 28,65</t>
+          <t>4,9; 29,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,43</t>
+          <t>0,0; 26,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 42,3</t>
+          <t>11,56; 39,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,02</t>
+          <t>0,0; 28,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 15,85</t>
+          <t>1,56; 15,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 23,87</t>
+          <t>4,91; 25,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,61</t>
+          <t>0,0; 19,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 25,37</t>
+          <t>7,7; 24,17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 22,18</t>
+          <t>6,12; 21,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 26,72</t>
+          <t>9,05; 26,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 28,16</t>
+          <t>5,18; 27,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,4</t>
+          <t>0,0; 14,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,54</t>
+          <t>0,0; 11,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,27; 31,67</t>
+          <t>11,55; 28,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 20,82</t>
+          <t>7,4; 20,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,76</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,75</t>
+          <t>0,77; 7,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 23,92</t>
+          <t>12,01; 24,46</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,86</t>
+          <t>2,6; 11,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,1</t>
+          <t>0,0; 28,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 27,7</t>
+          <t>6,36; 28,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,46</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 14,3</t>
+          <t>4,94; 14,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,55</t>
+          <t>0,0; 17,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 5,77</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,26</t>
+          <t>6,61; 12,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,6</t>
+          <t>2,62; 10,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,82</t>
+          <t>1,74; 5,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,25</t>
+          <t>7,27; 14,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,06</t>
+          <t>7,03; 15,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,28</t>
+          <t>0,88; 7,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>0,81; 5,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,77</t>
+          <t>6,68; 12,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,22</t>
+          <t>7,72; 12,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,74</t>
+          <t>2,42; 7,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,12</t>
+          <t>1,91; 4,95</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,19</t>
+          <t>7,54; 12,29</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2625</t>
         </is>
       </c>
     </row>
@@ -2209,27 +2209,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>962; 8936</t>
+          <t>964; 8784</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3639</t>
+          <t>0; 3749</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>910; 8366</t>
+          <t>895; 7865</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 4191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5563</t>
+          <t>0; 4442</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,32 +2239,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8230</t>
+          <t>0; 7953</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>170; 4224</t>
+          <t>545; 4324</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1911; 11201</t>
+          <t>1872; 10827</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4732</t>
+          <t>0; 4525</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2022; 11867</t>
+          <t>2031; 12868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>684; 6176</t>
+          <t>630; 6418</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6275</t>
         </is>
       </c>
     </row>
@@ -2417,32 +2417,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1895; 14450</t>
+          <t>1896; 14570</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6042</t>
+          <t>0; 6964</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1012; 8699</t>
+          <t>1017; 8521</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1161; 11039</t>
+          <t>1138; 10652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6005</t>
+          <t>0; 6878</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5144</t>
+          <t>0; 4220</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,27 +2452,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>716; 6059</t>
+          <t>721; 6107</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2969; 16350</t>
+          <t>3095; 15901</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6126</t>
+          <t>0; 6101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1019; 8575</t>
+          <t>1008; 8467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2276; 12779</t>
+          <t>2825; 14606</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15103</t>
         </is>
       </c>
     </row>
@@ -2625,27 +2625,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>970; 8571</t>
+          <t>1006; 8834</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 3647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3464; 13159</t>
+          <t>3543; 12766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6014</t>
+          <t>0; 6017</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2655,32 +2655,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>0; 4485</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4407; 12466</t>
+          <t>4381; 12371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1983; 11186</t>
+          <t>2054; 11863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5050</t>
+          <t>0; 5016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5277</t>
+          <t>0; 6232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9679; 22555</t>
+          <t>9406; 21368</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>826</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>6106</t>
         </is>
       </c>
     </row>
@@ -2833,32 +2833,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1019; 10081</t>
+          <t>978; 10083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4145</t>
+          <t>0; 4122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5402</t>
+          <t>0; 4823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 14112</t>
+          <t>0; 17596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6294</t>
+          <t>0; 7036</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>0; 3356</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>0; 4063</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2127; 12571</t>
+          <t>2125; 11351</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 6713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4584</t>
+          <t>0; 3727</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>612; 17037</t>
+          <t>948; 19250</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>863; 6777</t>
+          <t>850; 6864</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5900</t>
+          <t>0; 5277</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2724</t>
+          <t>0; 2572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5002</t>
+          <t>0; 4982</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1883; 10128</t>
+          <t>1832; 9892</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6306</t>
+          <t>0; 6155</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2921</t>
+          <t>0; 2728</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9525</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2097; 11978</t>
+          <t>2049; 12242</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6154</t>
+          <t>0; 6001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3977; 13374</t>
+          <t>3799; 12931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5077</t>
+          <t>0; 4038</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>467; 4790</t>
+          <t>478; 4600</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3063; 13345</t>
+          <t>2744; 14058</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6155</t>
+          <t>0; 5914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5038; 15687</t>
+          <t>4889; 15333</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>29155</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5543; 19614</t>
+          <t>5409; 18997</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3467,52 +3467,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7926</t>
+          <t>0; 7511</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5638; 19555</t>
+          <t>7772; 22883</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2953; 12261</t>
+          <t>2253; 11989</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6426</t>
+          <t>0; 6201</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7952; 22337</t>
+          <t>9320; 23367</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10096; 27484</t>
+          <t>9768; 27084</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>0; 4920</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1104; 10388</t>
+          <t>1035; 9921</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15262; 34374</t>
+          <t>19999; 40750</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1982</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2704; 12920</t>
+          <t>2835; 12167</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6332</t>
+          <t>0; 6435</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4050; 13789</t>
+          <t>3168; 14244</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5723</t>
+          <t>0; 6896</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7861; 22702</t>
+          <t>7834; 22354</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 6278</t>
+          <t>0; 6353</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 6654</t>
+          <t>0; 7164</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>39513</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>71351</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>32292; 57892</t>
+          <t>31212; 58423</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3708; 15108</t>
+          <t>3736; 14741</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6155; 20359</t>
+          <t>6088; 20082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26360; 51777</t>
+          <t>27991; 56998</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15931; 35361</t>
+          <t>15468; 33934</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>865; 7292</t>
+          <t>881; 7526</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1914; 12838</t>
+          <t>1754; 11305</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19415; 41707</t>
+          <t>23061; 43184</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>52127; 84594</t>
+          <t>53477; 84837</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5467; 18786</t>
+          <t>5871; 19125</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10465; 29009</t>
+          <t>10833; 28057</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50220; 84552</t>
+          <t>55032; 89745</t>
         </is>
       </c>
     </row>
